--- a/outputs/tablas/simulacion_mejoras_ot.xlsx
+++ b/outputs/tablas/simulacion_mejoras_ot.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="1086">
   <si>
     <t xml:space="preserve">metrica</t>
   </si>
@@ -3234,6 +3234,9 @@
   </si>
   <si>
     <t xml:space="preserve">Asignación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atención al client</t>
   </si>
   <si>
     <t xml:space="preserve">Clasificación de WO</t>
@@ -57111,13 +57114,13 @@
         <v>1071</v>
       </c>
       <c r="B9" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C9" t="n">
-        <v>3949.25</v>
+        <v>3943.13</v>
       </c>
       <c r="D9" t="n">
-        <v>3949.25</v>
+        <v>3943.13</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -57131,13 +57134,13 @@
         <v>1072</v>
       </c>
       <c r="B10" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1010.98</v>
+        <v>1.38</v>
       </c>
       <c r="D10" t="n">
-        <v>1010.98</v>
+        <v>1.38</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -57151,13 +57154,13 @@
         <v>1073</v>
       </c>
       <c r="B11" t="n">
-        <v>133</v>
+        <v>1000</v>
       </c>
       <c r="C11" t="n">
-        <v>585.21</v>
+        <v>1010.98</v>
       </c>
       <c r="D11" t="n">
-        <v>585.21</v>
+        <v>1010.98</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -57168,16 +57171,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1074</v>
+        <v>31</v>
       </c>
       <c r="B12" t="n">
-        <v>1080</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3823.72</v>
+        <v>6.12</v>
       </c>
       <c r="D12" t="n">
-        <v>3823.72</v>
+        <v>6.12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -57188,16 +57191,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B13" t="n">
-        <v>1133</v>
+        <v>133</v>
       </c>
       <c r="C13" t="n">
-        <v>2520.26</v>
+        <v>585.21</v>
       </c>
       <c r="D13" t="n">
-        <v>2520.26</v>
+        <v>585.21</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -57208,16 +57211,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B14" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="C14" t="n">
-        <v>993.11</v>
+        <v>3823.72</v>
       </c>
       <c r="D14" t="n">
-        <v>993.11</v>
+        <v>3823.72</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -57228,21 +57231,61 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1132</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2518.88</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2518.88</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
         <v>1077</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>1000</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="C16" t="n">
+        <v>993.11</v>
+      </c>
+      <c r="D16" t="n">
+        <v>993.11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -57262,25 +57305,25 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="E1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="2">
@@ -57403,25 +57446,25 @@
         <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="E1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="2">
@@ -57544,25 +57587,25 @@
         <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="E1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="2">

--- a/outputs/tablas/simulacion_mejoras_ot.xlsx
+++ b/outputs/tablas/simulacion_mejoras_ot.xlsx
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">Asignación</t>
   </si>
   <si>
-    <t xml:space="preserve">Atención al client</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clasificación de WO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalació</t>
   </si>
   <si>
     <t xml:space="preserve">Solicitud de información adicional</t>
@@ -57117,10 +57117,10 @@
         <v>999</v>
       </c>
       <c r="C9" t="n">
-        <v>3943.13</v>
+        <v>3940.12</v>
       </c>
       <c r="D9" t="n">
-        <v>3943.13</v>
+        <v>3940.12</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -57134,13 +57134,13 @@
         <v>1072</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="C10" t="n">
-        <v>1.38</v>
+        <v>1010.98</v>
       </c>
       <c r="D10" t="n">
-        <v>1.38</v>
+        <v>1010.98</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -57154,13 +57154,13 @@
         <v>1073</v>
       </c>
       <c r="B11" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1010.98</v>
+        <v>9.13</v>
       </c>
       <c r="D11" t="n">
-        <v>1010.98</v>
+        <v>9.13</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -57171,16 +57171,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>1074</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="C12" t="n">
-        <v>6.12</v>
+        <v>585.21</v>
       </c>
       <c r="D12" t="n">
-        <v>6.12</v>
+        <v>585.21</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -57191,16 +57191,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B13" t="n">
-        <v>133</v>
+        <v>1080</v>
       </c>
       <c r="C13" t="n">
-        <v>585.21</v>
+        <v>3823.72</v>
       </c>
       <c r="D13" t="n">
-        <v>585.21</v>
+        <v>3823.72</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -57211,16 +57211,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B14" t="n">
-        <v>1080</v>
+        <v>1133</v>
       </c>
       <c r="C14" t="n">
-        <v>3823.72</v>
+        <v>2520.26</v>
       </c>
       <c r="D14" t="n">
-        <v>3823.72</v>
+        <v>2520.26</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -57231,16 +57231,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B15" t="n">
-        <v>1132</v>
+        <v>1000</v>
       </c>
       <c r="C15" t="n">
-        <v>2518.88</v>
+        <v>993.11</v>
       </c>
       <c r="D15" t="n">
-        <v>2518.88</v>
+        <v>993.11</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -57251,41 +57251,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B16" t="n">
         <v>1000</v>
       </c>
       <c r="C16" t="n">
-        <v>993.11</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>993.11</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
         <v>0</v>
       </c>
     </row>

--- a/outputs/tablas/simulacion_mejoras_ot.xlsx
+++ b/outputs/tablas/simulacion_mejoras_ot.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="1085">
   <si>
     <t xml:space="preserve">metrica</t>
   </si>
@@ -3237,9 +3237,6 @@
   </si>
   <si>
     <t xml:space="preserve">Clasificación de WO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalació</t>
   </si>
   <si>
     <t xml:space="preserve">Solicitud de información adicional</t>
@@ -57114,13 +57111,13 @@
         <v>1071</v>
       </c>
       <c r="B9" t="n">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C9" t="n">
-        <v>3940.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D9" t="n">
-        <v>3940.12</v>
+        <v>3949.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -57154,13 +57151,13 @@
         <v>1073</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="C11" t="n">
-        <v>9.13</v>
+        <v>585.21</v>
       </c>
       <c r="D11" t="n">
-        <v>9.13</v>
+        <v>585.21</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -57174,13 +57171,13 @@
         <v>1074</v>
       </c>
       <c r="B12" t="n">
-        <v>133</v>
+        <v>1080</v>
       </c>
       <c r="C12" t="n">
-        <v>585.21</v>
+        <v>3823.72</v>
       </c>
       <c r="D12" t="n">
-        <v>585.21</v>
+        <v>3823.72</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -57194,13 +57191,13 @@
         <v>1075</v>
       </c>
       <c r="B13" t="n">
-        <v>1080</v>
+        <v>1133</v>
       </c>
       <c r="C13" t="n">
-        <v>3823.72</v>
+        <v>2520.26</v>
       </c>
       <c r="D13" t="n">
-        <v>3823.72</v>
+        <v>2520.26</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -57214,13 +57211,13 @@
         <v>1076</v>
       </c>
       <c r="B14" t="n">
-        <v>1133</v>
+        <v>1000</v>
       </c>
       <c r="C14" t="n">
-        <v>2520.26</v>
+        <v>993.11</v>
       </c>
       <c r="D14" t="n">
-        <v>2520.26</v>
+        <v>993.11</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -57237,35 +57234,15 @@
         <v>1000</v>
       </c>
       <c r="C15" t="n">
-        <v>993.11</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>993.11</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -57285,25 +57262,25 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C1" t="s">
         <v>1079</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1080</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1081</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1082</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1083</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1084</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="2">
@@ -57426,25 +57403,25 @@
         <v>14</v>
       </c>
       <c r="B1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C1" t="s">
         <v>1079</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1080</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1081</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1082</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1083</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1084</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="2">
@@ -57567,25 +57544,25 @@
         <v>16</v>
       </c>
       <c r="B1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C1" t="s">
         <v>1079</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1080</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1081</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1082</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1083</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1084</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="2">
